--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-at-prenudge-alcoholuse-valueset-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-at-prenudge-alcoholuse-valueset-frequency.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T15:14:29+00:00</t>
+    <t>2026-02-13T19:47:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-at-prenudge-alcoholuse-valueset-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-at-prenudge-alcoholuse-valueset-frequency.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T19:47:50+00:00</t>
+    <t>2026-02-22T11:57:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-at-prenudge-alcoholuse-valueset-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-at-prenudge-alcoholuse-valueset-frequency.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T11:57:51+00:00</t>
+    <t>2026-02-25T07:03:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-at-prenudge-alcoholuse-valueset-frequency.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-at-prenudge-alcoholuse-valueset-frequency.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/prenudge/appdata/r4/ValueSet/at-prenudge-alcoholuse-valueset-frequency</t>
+    <t>https://termgit.elga.gv.at/ValueSet/prenudge-alcoholuse-frequency</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T07:03:20+00:00</t>
+    <t>2026-02-26T10:01:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
